--- a/AAAGameData/DataTables/Item/ItemTable_Material.xlsx
+++ b/AAAGameData/DataTables/Item/ItemTable_Material.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="4560"/>
+    <workbookView windowWidth="19200" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -44,6 +44,12 @@
     <t>Identifier</t>
   </si>
   <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>MaxStack</t>
+  </si>
+  <si>
     <t>SpriteName</t>
   </si>
   <si>
@@ -56,13 +62,13 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>MaxStack</t>
-  </si>
-  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>enum</t>
   </si>
   <si>
     <r>
@@ -87,16 +93,22 @@
     </r>
   </si>
   <si>
-    <t>int[]</t>
+    <t>enum[]</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>在代码中的命名标识符(下划线前与表名一致)</t>
-  </si>
-  <si>
-    <t>Sprite名</t>
+    <t>在代码中的命名标识符</t>
+  </si>
+  <si>
+    <t>品质</t>
+  </si>
+  <si>
+    <t>最大堆叠数(-1表示无限)</t>
+  </si>
+  <si>
+    <t>Sprite路径</t>
   </si>
   <si>
     <t>物品名(多语言)</t>
@@ -108,61 +120,85 @@
     <t>物品类型标签</t>
   </si>
   <si>
-    <t>最大堆叠数(-1表示无限)</t>
-  </si>
-  <si>
-    <t>Material_aaa</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>Item.Material.Name1</t>
-  </si>
-  <si>
-    <t>Item.Material.Description1</t>
-  </si>
-  <si>
-    <t>Material_bbb</t>
-  </si>
-  <si>
-    <t>Item.Material.Name2</t>
-  </si>
-  <si>
-    <t>Item.Material.Description2</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>Material_ccc</t>
-  </si>
-  <si>
-    <t>Item.Material.Name3</t>
-  </si>
-  <si>
-    <t>Item.Material.Description3</t>
-  </si>
-  <si>
-    <t>Material_ddd</t>
-  </si>
-  <si>
-    <t>Item.Material.Name4</t>
-  </si>
-  <si>
-    <t>Item.Material.Description4</t>
-  </si>
-  <si>
-    <t>Material_eee</t>
-  </si>
-  <si>
-    <t>Item.Material.Name5</t>
-  </si>
-  <si>
-    <t>Item.Material.Description5</t>
-  </si>
-  <si>
-    <t>0,1,3</t>
+    <t>Material_Aaa</t>
+  </si>
+  <si>
+    <t>ItemRarity.Common</t>
+  </si>
+  <si>
+    <t>UI/IconMisc/Icon_Star_On.png</t>
+  </si>
+  <si>
+    <t>Item.Material.Name.Aaa</t>
+  </si>
+  <si>
+    <t>Item.Material.Description.Aaa</t>
+  </si>
+  <si>
+    <t>ItemTag.AAA</t>
+  </si>
+  <si>
+    <t>Material_Bbb</t>
+  </si>
+  <si>
+    <t>ItemRarity.Rare</t>
+  </si>
+  <si>
+    <t>UI/IconMisc/Icon_Star_Off.png</t>
+  </si>
+  <si>
+    <t>Item.Material.Name.Bbb</t>
+  </si>
+  <si>
+    <t>Item.Material.Description.Bbb</t>
+  </si>
+  <si>
+    <t>ItemTag.BBB,ItemTag.AAA</t>
+  </si>
+  <si>
+    <t>Material_Ccc</t>
+  </si>
+  <si>
+    <t>ItemRarity.Epic</t>
+  </si>
+  <si>
+    <t>UI/IconMisc/Icon_Setting.png</t>
+  </si>
+  <si>
+    <t>Item.Material.Name.Ccc</t>
+  </si>
+  <si>
+    <t>Item.Material.Description.Ccc</t>
+  </si>
+  <si>
+    <t>Material_Ddd</t>
+  </si>
+  <si>
+    <t>ItemRarity.Legendary</t>
+  </si>
+  <si>
+    <t>UI/IconMisc/Icon_Close02.png</t>
+  </si>
+  <si>
+    <t>Item.Material.Name.Ddd</t>
+  </si>
+  <si>
+    <t>Item.Material.Description.Ddd</t>
+  </si>
+  <si>
+    <t>Material_Eee</t>
+  </si>
+  <si>
+    <t>ItemRarity.Heroic</t>
+  </si>
+  <si>
+    <t>UI/IconMisc/Icon_Check03_s.png</t>
+  </si>
+  <si>
+    <t>Item.Material.Name.Eee</t>
+  </si>
+  <si>
+    <t>Item.Material.Description.Eee</t>
   </si>
 </sst>
 </file>
@@ -522,12 +558,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="5" tint="0.6"/>
+      </left>
+      <right style="medium">
+        <color theme="5" tint="0.6"/>
+      </right>
+      <top style="medium">
+        <color theme="5" tint="0.6"/>
+      </top>
+      <bottom style="medium">
+        <color theme="5" tint="0.6"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -652,7 +703,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -664,34 +715,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -776,8 +827,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1097,225 +1151,251 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75"/>
   <cols>
-    <col min="1" max="1" width="2.5" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="5.125" customWidth="1"/>
-    <col min="4" max="4" width="38.125" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="17.5" customWidth="1"/>
-    <col min="7" max="7" width="25.375" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.8333333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="22.4166666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.5833333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="29.9166666666667" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I3" t="s">
-        <v>10</v>
+      <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I4" t="s">
+      <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="B5">
+    <row r="5" ht="28.75" spans="2:10">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="28.75" spans="2:10">
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="28.75" spans="2:10">
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" ht="28.75" spans="2:10">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="1">
         <v>-1</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="D7" t="s">
+    <row r="9" ht="28.75" spans="2:10">
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
-      </c>
-      <c r="I7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="I8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Item/ItemTable_Material.xlsx
+++ b/AAAGameData/DataTables/Item/ItemTable_Material.xlsx
@@ -53,10 +53,10 @@
     <t>SpriteName</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
+    <t>NameKey</t>
+  </si>
+  <si>
+    <t>DescriptionKey</t>
   </si>
   <si>
     <t>Tags</t>
@@ -1279,7 +1279,7 @@
         <v>25</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>26</v>
@@ -1305,7 +1305,7 @@
         <v>31</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>32</v>
